--- a/extenbooks/ES1102.xlsx
+++ b/extenbooks/ES1102.xlsx
@@ -793,7 +793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -957,7 +957,7 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t># ES1102 — Social Benefit Rate (ST 1987) — PENDING</t>
+          <t># ES1102 — Social Benefit Rate (S&amp;T 1987)</t>
         </is>
       </c>
     </row>
@@ -969,87 +969,31 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>**Chapter**: External study</t>
+          <t>**Status**: book_period_validated. Derived: `(S605 + S606) / S617`. Range 1952-1989: [0.2162, 0.3493]. Workers receive 22-35% of total compensation back as benefits + government services.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>**Status**: pending_data_assembly</t>
-        </is>
-      </c>
+      <c r="B19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>## Why pending</t>
-        </is>
-      </c>
+      <c r="B21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>derived from Ch6</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>## Activation path</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Compute (B_w + G_w) / EC using S605, S606 + employee compensation</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>*Generated by anu-ingestion (pending stub).*</t>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>*Generated by anu-ingestion.*</t>
         </is>
       </c>
     </row>

--- a/extenbooks/ES1102.xlsx
+++ b/extenbooks/ES1102.xlsx
@@ -793,11 +793,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="43" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -844,7 +844,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Study 2</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1952–1985</t>
+          <t>1952-1989</t>
         </is>
       </c>
     </row>
@@ -946,52 +946,73 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Subseries</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>source / role</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ES1102-A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Shaikh &amp; Tonak 1987</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t># ES1102 — Social Benefit Rate (S&amp;T 1987)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>**Status**: book_period_validated. Derived: `(S605 + S606) / S617`. Range 1952-1989: [0.2162, 0.3493]. Workers receive 22-35% of total compensation back as benefits + government services.</t>
-        </is>
-      </c>
+      <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t># ES1102 — Social Benefit Rate (S&amp;T 1987)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>**Status**: book_period_validated</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
         <is>
           <t>*Generated by anu-ingestion.*</t>
         </is>
@@ -1008,10 +1029,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="62" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1036,279 +1057,418 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>methodology_description</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Social benefit rate = Benefits received by workers from the state / Apparent wage (employee compensation). Formula: B_w / EC. This measures social welfare expenditures directed to workers as a fraction of total employee compensation. Benefits (B_w) are composed of Group I items (directed 100% to workers: income support, social security and welfare excluding military disability and retirement, housing and community services, labor training and services) plus the labor share of Group II items (education, health and hospitals, recreational and cultural activities, energy, natural resources, transportation adjusted by gas share of passenger cars, postal services). Transportation within Group II is additionally adjusted by the 'Gas Share of Passenger Cars' factor from Tonak (1984, Appendix II). Labor share = total labor income / personal income (example 1964: 0.73).</t>
+          <t>VERBATIM (Shaikh &amp; Tonak 1987, Group II classification, p.187): "Conventional categories treated as social consumption in general, with workers' share estimated by multiplying group total by share of total labor income in personal income ... Estimation Method: Workers' share = (Total labor income / Personal income) x Group II total." This is the labor-share allocation rule that ES1102 must implement on Group II expenditures (Education, Health and Hospitals, Recreational, Energy, Natural Resources, Transportation, Postal Services). Comes from the external paper.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md (Empirical Methodology pp.186-187; Classification of Government Expenditures; Appendix Table 1 pp.191-192; Key Formulas — Benefit Rate)</t>
+          <t>1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md (Classification of Government Expenditures, GROUP II: Social Consumption, lines 188-200)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>data_source</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Primary source: Shaikh and Tonak (1987). The benefit rate is derived from the benefits column of Table 2 ('Expenditures Received and Taxes Paid by Labor — Net Transfer, 1952-85', p.192) divided by total employee compensation from BEA NIPA. Appendix Table 1 (p.191) illustrates the full benefit calculation for 1964: Group I total (income support 29.7 + housing 2.81 + labor training 0.73 = 33.24) plus labor-share-allocated Group II total (education 20.13 + health 4.69 + recreational 0.88 + energy 0.75 + natural resources 1.43 + postal 0.58 + transportation 6.31 = 34.77), summing to 68.01 billion in 1964. BEA Social Welfare Expenditure data from BEA (1981:151, 159).</t>
+          <t>VERBATIM (Shaikh &amp; Tonak 1987, GROUP I note, p.187): "Included: Labor Training and Services; Housing and Community Services; Income Support; Social Security and Welfare (except Military Disability and Military Retirement). Note: Military Disability and Military Retirement are treated as a cost of war and excluded." This precisely defines the Group I content (100% to workers) and the military-retirement exclusion rule that S605 must enforce or ES1102 will be overstated.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md (Appendix Table 1 pp.191-192; Table 2 p.192; Data Sources)</t>
+          <t>1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md (Classification of Government Expenditures, GROUP I: Direct Benefits to Workers, lines 178-186)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>empirical_values</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Key benchmark values from Figure 2 time series (benefits as proportion of employee compensation): 1952 approx 11%; rises steadily to approximately 20% by 1968; accelerates sharply to approximately 33% by 1975 (peak); stabilizes around 31% from 1975-1980; declines to approximately 20% by 1984. By 1985 the benefit rate falls below the 1966 reference level. Absolute dollar values from Table 2: 1952=21.01B, 1964=68.01B, 1975=289.12B, 1985=467.83B.</t>
+          <t>VERBATIM (Shaikh &amp; Tonak 1987, Figure 2 description, p.188): "Benefit Rate: 1952 approx 0.11 (11%); rises steadily to 1968 approx 0.20 (20%); 1968-1975: Accelerates to approx 0.33 (33%); 1975-1980: Stabilizes around 0.31 (31%)." Combined with the Phase 3 finding that "by 1985 the social benefit rate is at a level below that of 1966," this provides the full ES1102 trajectory shape (1952 floor, 1975 peak, 1985 collapse) for validation against P19 output.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md (Figure 2 description pp.188; Key Formulas — Benefit Rate; Table 2 p.192)</t>
+          <t>1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md (Figure 2 description, Benefit Rate, lines 317-321; Phase 3 Critical Finding for 1985, line 493)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>expenditure_classification</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Group I (100% to workers, direct benefits): Labor Training and Services; Housing and Community Services; Income Support; Social Security and Welfare (excluding Military Disability and Military Retirement, which are treated as costs of war). Group II (allocated by labor share): Education; Health and Hospitals; Recreational and Cultural Activities; Energy; Natural Resources; Transportation (with additional Gas Share adjustment); Postal Services. Group III (excluded entirely — system reproduction costs): Central Executive/Legislative/Judicial; International Affairs; Space; National Defense; Civilian Safety; Veteran Benefits; Agriculture; Economic Development; Regulation and Services; Net Interest; Others and Unallocables.</t>
+          <t>Social Welfare Expenditures (to workers): = Group I (direct benefits) + Labor's share of Group II (social consumption) Where labor's share = (Total labor income / Personal income)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md (Classification of Government Expenditures pp.186-187)</t>
+          <t>Shaikh &amp; Tonak 1987, Empirical Methodology, p.187</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>caveat</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The benefit rate (ES1102) includes public assistance (welfare payments) in Group I. The authors note (Note 12) that public assistance is appropriate for measuring overall worker living standards but must be excluded when computing the rate of exploitation adjustment, since public assistance recipients are not employed workers. The registered ES1102 series is the living-standards measure (public assistance included). Do not use ES1102 directly in surplus value rate calculations — use the productive-worker variant from Tonak (1984) Chapter IV Table XII instead.</t>
+          <t>It is striking that by 1985 the social benefit rate is at a level below that of 1966</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md (Note 12, pp.193-194)</t>
+          <t>Shaikh &amp; Tonak 1987, Phase 3 analysis, p.190</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>caveat</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Military Disability and Military Retirement payments are explicitly excluded from Group I benefits despite appearing in Social Security and Welfare NIPA categories. The authors treat these as costs of war, not worker welfare benefits. If the underlying NIPA data aggregation includes these items without adjustment, the benefit rate will be overstated. Researchers computing ES1102 from S605 must verify that S605 excludes military disability and retirement.</t>
+          <t>Benefit Rate: 1952: ~0.11 (11%) ... Rises steadily to 1968: ~0.20 (20%) ... 1968-1975: Accelerates to ~0.33 (33%) ... 1975-1980: Stabilizes around 0.31 (31%) ... 1980-1984: Declines to ~0.20 (20%)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md (Classification of Government Expenditures — GROUP I note)</t>
+          <t>Shaikh &amp; Tonak 1987, Figure 2, p.188</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>caveat</t>
+          <t>methodology_description</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The labor share allocation applied to Group II expenditures is an approximation based on the ratio of total labor income to personal income. This assumes workers' consumption of social services (education, health, etc.) is proportional to their income share. The actual incidence may differ across income groups, regions, and service types. The transportation item requires an additional adjustment (Gas Share of Passenger Cars from Tonak 1984 Appendix II) that has its own estimation uncertainty.</t>
+          <t>Social benefit rate = Benefits received by workers from the state / Apparent wage (employee compensation). Formula: B_w / EC. This measures social welfare expenditures directed to workers as a fraction of total employee compensation. Benefits (B_w) are composed of Group I items (directed 100% to workers: income support, social security and welfare excluding military disability and retirement, housing and community services, labor training and services) plus the labor share of Group II items (education, health and hospitals, recreational and cultural activities, energy, natural resources, transportation adjusted by gas share of passenger cars, postal services). Transportation within Group II is additionally adjusted by the 'Gas Share of Passenger Cars' factor from Tonak (1984, Appendix II). Labor share = total labor income / personal income (example 1964: 0.73).</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md (Empirical Methodology p.186-187; Appendix Table 1 footnote b)</t>
+          <t>1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md (Empirical Methodology pp.186-187; Classification of Government Expenditures; Appendix Table 1 pp.191-192; Key Formulas — Benefit Rate)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>decision_reference</t>
+          <t>data_source</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DEC-012 (No Synthetic Data Policy, 2026-05-03): ES1102 is not listed among the five series requiring synthetic-data remediation. However, if S605 (benefits received by workers) contains synthetic or estimated data, ES1102 inherits that status. The 34-year series in S&amp;T (1987) Table 2 column 1 (benefits column) provides direct validation benchmarks for P19 S605 output. These should be used as V-layer checks.</t>
+          <t>Primary source: Shaikh and Tonak (1987). The benefit rate is derived from the benefits column of Table 2 ('Expenditures Received and Taxes Paid by Labor — Net Transfer, 1952-85', p.192) divided by total employee compensation from BEA NIPA. Appendix Table 1 (p.191) illustrates the full benefit calculation for 1964: Group I total (income support 29.7 + housing 2.81 + labor training 0.73 = 33.24) plus labor-share-allocated Group II total (education 20.13 + health 4.69 + recreational 0.88 + energy 0.75 + natural resources 1.43 + postal 0.58 + transportation 6.31 = 34.77), summing to 68.01 billion in 1964. BEA Social Welfare Expenditure data from BEA (1981:151, 159).</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DECISION_LOG.md#DEC-012</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
+          <t>1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md (Appendix Table 1 pp.191-192; Table 2 p.192; Data Sources)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>empirical_values</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Key benchmark values from Figure 2 time series (benefits as proportion of employee compensation): 1952 approx 11%; rises steadily to approximately 20% by 1968; accelerates sharply to approximately 33% by 1975 (peak); stabilizes around 31% from 1975-1980; declines to approximately 20% by 1984. By 1985 the benefit rate falls below the 1966 reference level. Absolute dollar values from Table 2: 1952=21.01B, 1964=68.01B, 1975=289.12B, 1985=467.83B.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md (Figure 2 description pp.188; Key Formulas — Benefit Rate; Table 2 p.192)</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>methodology_summary</t>
+          <t>expenditure_classification</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Social benefit rate = B_w / EC, 1952-1985 (34 years). Benefits include direct worker benefits (Group I, 100% allocation) plus labor share of social consumption (Group II). Key benchmarks: ~11% (1952), ~33% peak (1975), below 1966 level (~20%) by 1985.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
+          <t>Group I (100% to workers, direct benefits): Labor Training and Services; Housing and Community Services; Income Support; Social Security and Welfare (excluding Military Disability and Military Retirement, which are treated as costs of war). Group II (allocated by labor share): Education; Health and Hospitals; Recreational and Cultural Activities; Energy; Natural Resources; Transportation (with additional Gas Share adjustment); Postal Services. Group III (excluded entirely — system reproduction costs): Central Executive/Legislative/Judicial; International Affairs; Space; National Defense; Civilian Safety; Veteran Benefits; Agriculture; Economic Development; Regulation and Services; Net Interest; Others and Unallocables.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md (Classification of Government Expenditures pp.186-187)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>caveat</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>The benefit rate (ES1102) includes public assistance (welfare payments) in Group I. The authors note (Note 12) that public assistance is appropriate for measuring overall worker living standards but must be excluded when computing the rate of exploitation adjustment, since public assistance recipients are not employed workers. The registered ES1102 series is the living-standards measure (public assistance included). Do not use ES1102 directly in surplus value rate calculations — use the productive-worker variant from Tonak (1984) Chapter IV Table XII instead.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md (Note 12, pp.193-194)</t>
+        </is>
+      </c>
+    </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>known_issues:</t>
+          <t>caveat</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Military Disability and Military Retirement payments are explicitly excluded from Group I benefits despite appearing in Social Security and Welfare NIPA categories. The authors treat these as costs of war, not worker welfare benefits. If the underlying NIPA data aggregation includes these items without adjustment, the benefit rate will be overstated. Researchers computing ES1102 from S605 must verify that S605 excludes military disability and retirement.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md (Classification of Government Expenditures — GROUP I note)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>caveat</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Public assistance included — not appropriate for exploitation rate adjustment</t>
+          <t>The labor share allocation applied to Group II expenditures is an approximation based on the ratio of total labor income to personal income. This assumes workers' consumption of social services (education, health, etc.) is proportional to their income share. The actual incidence may differ across income groups, regions, and service types. The transportation item requires an additional adjustment (Gas Share of Passenger Cars from Tonak 1984 Appendix II) that has its own estimation uncertainty.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md (Empirical Methodology p.186-187; Appendix Table 1 footnote b)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>decision_reference</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Military disability/retirement must be excluded from NIPA Social Security aggregates in S605</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Transportation allocation requires Gas Share of Passenger Cars adjustment from Tonak 1984 Appendix II</t>
-        </is>
-      </c>
-    </row>
+          <t>[internal-decision-record] (No Synthetic Data Policy, 2026-05-03): ES1102 is not listed among the five series requiring synthetic-data remediation. However, if S605 (benefits received by workers) contains synthetic or estimated data, ES1102 inherits that status. The 34-year series in S&amp;T (1987) Table 2 column 1 (benefits column) provides direct validation benchmarks for P19 S605 output. These should be used as V-layer checks.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[internal-decision-log]#[internal-decision-record]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Labor share allocation is a proportional approximation of actual incidence</t>
-        </is>
-      </c>
-    </row>
-    <row r="18"/>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>VERBATIM QUOTES (top-level)</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr"/>
+      <c r="C17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Social Welfare Expenditures (to workers): = Group I (direct benefits) + Labor's share of Group II (social consumption) Where labor's share = (Total labor income / Personal income)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+    </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>cross_references:</t>
-        </is>
-      </c>
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>It is striking that by 1985 the social benefit rate is at a level below that of 1966</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
+          <t>Benefit Rate: 1952: ~0.11 (11%) ... Rises steadily to 1968: ~0.20 (20%) ... 1968-1975: Accelerates to ~0.33 (33%) ... 1975-1980: Stabilizes around 0.31 (31%) ... 1980-1984: Declines to ~0.20 (20%)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>methodology_summary</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Social benefit rate = B_w / EC, 1952-1985 (34 years). Benefits include direct worker benefits (Group I, 100% allocation) plus labor share of social consumption (Group II). Key benchmarks: ~11% (1952), ~33% peak (1975), below 1966 level (~20%) by 1985.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>known_issues:</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Public assistance included — not appropriate for exploitation rate adjustment</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Military disability/retirement must be excluded from NIPA Social Security aggregates in S605</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Transportation allocation requires Gas Share of Passenger Cars adjustment from Tonak 1984 Appendix II</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Labor share allocation is a proportional approximation of actual incidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>cross_references:</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
           <t>ES1001</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
         <is>
           <t>ES1002</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
         <is>
           <t>ES1101</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
         <is>
           <t>ES1103</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
         <is>
           <t>S605</t>
         </is>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>citations:</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>ST_1987</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>Shaikh, Anwar, and E. Ahmet Tonak. 1987. 'The Welfare State and the Myth of the Social Wage.' In Robert Cherry et al. (eds.), The Imperiled Economy, Book I. New York: Union for Radical Political Economics, pp. 184-194.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>BEA_1981</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>Bureau of Economic Analysis. 1981. Survey of Current Business. Tables at pp. 151, 159 (social welfare expenditures).</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Tonak_1984</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>Tonak, Ertugrul Ahmet. 1984. 'A Conceptualization of State Revenues and Expenditures U.S.: 1952-1980.' PhD Dissertation, New School for Social Research. UMI Order Number 9414212.</t>
         </is>
@@ -1325,11 +1485,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
@@ -1396,7 +1556,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>null — series does not extend beyond book period</t>
+          <t>null - series does not extend beyond book period</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1577,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"1952": 0.11, "1968": 0.2, "1975": 0.33, "1980": 0.31, "1984": 0.2}</t>
         </is>
       </c>
     </row>
@@ -1441,7 +1601,43 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>rate_series</t>
+          <t>share_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>tolerance_class</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>share_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>tolerance_rel</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>tolerance_abs</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0.01</t>
         </is>
       </c>
     </row>
